--- a/Java25 NguyenMinhDuy Database Design.xlsx
+++ b/Java25 NguyenMinhDuy Database Design.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qphan\Desktop\bkit\course - plan and doc\Phần 3 - Database(MySQL)\16. RBDMS\DEMO\RDBMS demo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java25\3.Database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4387BC7E-9F9D-4AE6-8B47-86972CA1DD05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85807147-DFD6-49B1-81E0-699218690289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="3900" windowWidth="21600" windowHeight="12645" tabRatio="588" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="588" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mô hình quan niệm" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="265">
   <si>
     <t>MatHang</t>
   </si>
@@ -837,12 +837,120 @@
   <si>
     <t>Trigger, View</t>
   </si>
+  <si>
+    <t>Mặt hàng</t>
+  </si>
+  <si>
+    <t>Mã mặt hàng</t>
+  </si>
+  <si>
+    <t>Tên mặt hàng</t>
+  </si>
+  <si>
+    <t>Kích thước</t>
+  </si>
+  <si>
+    <t>Giá mua</t>
+  </si>
+  <si>
+    <t>Giá bán</t>
+  </si>
+  <si>
+    <t>Loại sản phẩm</t>
+  </si>
+  <si>
+    <t>Chất liệu</t>
+  </si>
+  <si>
+    <t>Màu sắc</t>
+  </si>
+  <si>
+    <t>Hình ảnh</t>
+  </si>
+  <si>
+    <t>Loại hàng</t>
+  </si>
+  <si>
+    <t>Mã loại hàng</t>
+  </si>
+  <si>
+    <t>Tên loại hàng</t>
+  </si>
+  <si>
+    <t>Nhóm hàng</t>
+  </si>
+  <si>
+    <t>Mã nhóm hàng</t>
+  </si>
+  <si>
+    <t>Tên nhóm hàng</t>
+  </si>
+  <si>
+    <t>Đơn hàng</t>
+  </si>
+  <si>
+    <t>Mã đơn hàng</t>
+  </si>
+  <si>
+    <t>Ngày đặt</t>
+  </si>
+  <si>
+    <t>Tổng số lượng</t>
+  </si>
+  <si>
+    <t>Tổng tiền</t>
+  </si>
+  <si>
+    <t>Phí vận chuyển</t>
+  </si>
+  <si>
+    <t>Chi tiết đơn hàng</t>
+  </si>
+  <si>
+    <t>Số lượng</t>
+  </si>
+  <si>
+    <t>Tài khoản</t>
+  </si>
+  <si>
+    <t>Tên đăng nhập</t>
+  </si>
+  <si>
+    <t>Mật khẩu</t>
+  </si>
+  <si>
+    <t>Trạng thái đơn hàng</t>
+  </si>
+  <si>
+    <t>Mã trạng thái</t>
+  </si>
+  <si>
+    <t>Tên trạng thái</t>
+  </si>
+  <si>
+    <t>Thời gian cập nhập</t>
+  </si>
+  <si>
+    <t>Nhân viên</t>
+  </si>
+  <si>
+    <t>Mã nhân viên</t>
+  </si>
+  <si>
+    <t>Họ tên</t>
+  </si>
+  <si>
+    <t>Chức vụ</t>
+  </si>
+  <si>
+    <t>Số điện thoại</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -931,6 +1039,17 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="12">
@@ -1048,7 +1167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1204,6 +1323,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1534,223 +1662,420 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B4:K24"/>
+  <dimension ref="A2:N24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
-    <col min="2" max="3" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="14.140625" customWidth="1"/>
-    <col min="6" max="8" width="12.7109375" customWidth="1"/>
+    <col min="6" max="6" width="19.28515625" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" customWidth="1"/>
+    <col min="8" max="8" width="18.140625" customWidth="1"/>
     <col min="9" max="9" width="19.28515625" customWidth="1"/>
     <col min="10" max="20" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-    </row>
-    <row r="5" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-    </row>
-    <row r="6" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-    </row>
-    <row r="7" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-    </row>
-    <row r="9" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-    </row>
-    <row r="10" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-    </row>
-    <row r="11" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-    </row>
-    <row r="12" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-    </row>
-    <row r="13" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-    </row>
-    <row r="14" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-    </row>
-    <row r="15" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-    </row>
-    <row r="16" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-    </row>
-    <row r="17" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-    </row>
-    <row r="18" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-    </row>
-    <row r="19" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-    </row>
-    <row r="20" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-    </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="60"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="60"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="60"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="60"/>
+      <c r="K3" s="60"/>
+      <c r="L3" s="60"/>
+      <c r="M3" s="60"/>
+      <c r="N3" s="60"/>
+    </row>
+    <row r="4" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="60"/>
+      <c r="B4" s="61" t="s">
+        <v>229</v>
+      </c>
+      <c r="C4" s="61" t="s">
+        <v>239</v>
+      </c>
+      <c r="D4" s="61" t="s">
+        <v>242</v>
+      </c>
+      <c r="E4" s="61" t="s">
+        <v>245</v>
+      </c>
+      <c r="F4" s="61" t="s">
+        <v>251</v>
+      </c>
+      <c r="G4" s="61" t="s">
+        <v>253</v>
+      </c>
+      <c r="H4" s="61" t="s">
+        <v>256</v>
+      </c>
+      <c r="I4" s="61" t="s">
+        <v>260</v>
+      </c>
+      <c r="J4" s="62"/>
+      <c r="K4" s="62"/>
+      <c r="L4" s="60"/>
+      <c r="M4" s="60"/>
+      <c r="N4" s="60"/>
+    </row>
+    <row r="5" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="60"/>
+      <c r="B5" s="63" t="s">
+        <v>230</v>
+      </c>
+      <c r="C5" s="63" t="s">
+        <v>240</v>
+      </c>
+      <c r="D5" s="63" t="s">
+        <v>243</v>
+      </c>
+      <c r="E5" s="63" t="s">
+        <v>246</v>
+      </c>
+      <c r="F5" s="63" t="s">
+        <v>246</v>
+      </c>
+      <c r="G5" s="63" t="s">
+        <v>254</v>
+      </c>
+      <c r="H5" s="63" t="s">
+        <v>257</v>
+      </c>
+      <c r="I5" s="63" t="s">
+        <v>261</v>
+      </c>
+      <c r="J5" s="64"/>
+      <c r="K5" s="64"/>
+      <c r="L5" s="60"/>
+      <c r="M5" s="60"/>
+      <c r="N5" s="60"/>
+    </row>
+    <row r="6" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="60"/>
+      <c r="B6" s="63" t="s">
+        <v>231</v>
+      </c>
+      <c r="C6" s="63" t="s">
+        <v>241</v>
+      </c>
+      <c r="D6" s="63" t="s">
+        <v>244</v>
+      </c>
+      <c r="E6" s="63" t="s">
+        <v>247</v>
+      </c>
+      <c r="F6" s="63" t="s">
+        <v>230</v>
+      </c>
+      <c r="G6" s="63" t="s">
+        <v>255</v>
+      </c>
+      <c r="H6" s="63" t="s">
+        <v>258</v>
+      </c>
+      <c r="I6" s="63" t="s">
+        <v>262</v>
+      </c>
+      <c r="J6" s="64"/>
+      <c r="K6" s="64"/>
+      <c r="L6" s="60"/>
+      <c r="M6" s="60"/>
+      <c r="N6" s="60"/>
+    </row>
+    <row r="7" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="60"/>
+      <c r="B7" s="63" t="s">
+        <v>232</v>
+      </c>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="63" t="s">
+        <v>248</v>
+      </c>
+      <c r="F7" s="63" t="s">
+        <v>252</v>
+      </c>
+      <c r="G7" s="64"/>
+      <c r="H7" s="63" t="s">
+        <v>259</v>
+      </c>
+      <c r="I7" s="63" t="s">
+        <v>263</v>
+      </c>
+      <c r="J7" s="64"/>
+      <c r="K7" s="64"/>
+      <c r="L7" s="60"/>
+      <c r="M7" s="60"/>
+      <c r="N7" s="60"/>
+    </row>
+    <row r="8" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="60"/>
+      <c r="B8" s="63" t="s">
+        <v>233</v>
+      </c>
+      <c r="C8" s="64"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="63" t="s">
+        <v>249</v>
+      </c>
+      <c r="F8" s="63" t="s">
+        <v>237</v>
+      </c>
+      <c r="G8" s="64"/>
+      <c r="H8" s="64"/>
+      <c r="I8" s="63" t="s">
+        <v>264</v>
+      </c>
+      <c r="J8" s="64"/>
+      <c r="K8" s="64"/>
+      <c r="L8" s="60"/>
+      <c r="M8" s="60"/>
+      <c r="N8" s="60"/>
+    </row>
+    <row r="9" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="60"/>
+      <c r="B9" s="63" t="s">
+        <v>234</v>
+      </c>
+      <c r="C9" s="64"/>
+      <c r="D9" s="64"/>
+      <c r="E9" s="63" t="s">
+        <v>250</v>
+      </c>
+      <c r="F9" s="64"/>
+      <c r="G9" s="64"/>
+      <c r="H9" s="64"/>
+      <c r="I9" s="64"/>
+      <c r="J9" s="64"/>
+      <c r="K9" s="64"/>
+      <c r="L9" s="60"/>
+      <c r="M9" s="60"/>
+      <c r="N9" s="60"/>
+    </row>
+    <row r="10" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="60"/>
+      <c r="B10" s="63" t="s">
+        <v>235</v>
+      </c>
+      <c r="C10" s="64"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="64"/>
+      <c r="H10" s="64"/>
+      <c r="I10" s="64"/>
+      <c r="J10" s="64"/>
+      <c r="K10" s="64"/>
+      <c r="L10" s="60"/>
+      <c r="M10" s="60"/>
+      <c r="N10" s="60"/>
+    </row>
+    <row r="11" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="60"/>
+      <c r="B11" s="63" t="s">
+        <v>236</v>
+      </c>
+      <c r="C11" s="64"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="64"/>
+      <c r="H11" s="64"/>
+      <c r="I11" s="64"/>
+      <c r="J11" s="64"/>
+      <c r="K11" s="64"/>
+      <c r="L11" s="60"/>
+      <c r="M11" s="60"/>
+      <c r="N11" s="60"/>
+    </row>
+    <row r="12" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="60"/>
+      <c r="B12" s="63" t="s">
+        <v>237</v>
+      </c>
+      <c r="C12" s="64"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="64"/>
+      <c r="H12" s="64"/>
+      <c r="I12" s="64"/>
+      <c r="J12" s="64"/>
+      <c r="K12" s="64"/>
+      <c r="L12" s="60"/>
+      <c r="M12" s="60"/>
+      <c r="N12" s="60"/>
+    </row>
+    <row r="13" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="60"/>
+      <c r="B13" s="63" t="s">
+        <v>238</v>
+      </c>
+      <c r="C13" s="64"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="64"/>
+      <c r="G13" s="64"/>
+      <c r="H13" s="64"/>
+      <c r="I13" s="64"/>
+      <c r="J13" s="64"/>
+      <c r="K13" s="64"/>
+      <c r="L13" s="60"/>
+      <c r="M13" s="60"/>
+      <c r="N13" s="60"/>
+    </row>
+    <row r="14" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="60"/>
+      <c r="B14" s="64"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="64"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="64"/>
+      <c r="G14" s="64"/>
+      <c r="H14" s="64"/>
+      <c r="I14" s="64"/>
+      <c r="J14" s="64"/>
+      <c r="K14" s="64"/>
+      <c r="L14" s="60"/>
+      <c r="M14" s="60"/>
+      <c r="N14" s="60"/>
+    </row>
+    <row r="15" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="60"/>
+      <c r="B15" s="64"/>
+      <c r="C15" s="64"/>
+      <c r="D15" s="64"/>
+      <c r="E15" s="64"/>
+      <c r="F15" s="64"/>
+      <c r="G15" s="64"/>
+      <c r="H15" s="64"/>
+      <c r="I15" s="64"/>
+      <c r="J15" s="64"/>
+      <c r="K15" s="64"/>
+      <c r="L15" s="60"/>
+      <c r="M15" s="60"/>
+      <c r="N15" s="60"/>
+    </row>
+    <row r="16" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="60"/>
+      <c r="B16" s="64"/>
+      <c r="C16" s="64"/>
+      <c r="D16" s="64"/>
+      <c r="E16" s="64"/>
+      <c r="F16" s="64"/>
+      <c r="G16" s="64"/>
+      <c r="H16" s="64"/>
+      <c r="I16" s="64"/>
+      <c r="J16" s="64"/>
+      <c r="K16" s="64"/>
+      <c r="L16" s="60"/>
+      <c r="M16" s="60"/>
+      <c r="N16" s="60"/>
+    </row>
+    <row r="17" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="60"/>
+      <c r="B17" s="64"/>
+      <c r="C17" s="64"/>
+      <c r="D17" s="64"/>
+      <c r="E17" s="64"/>
+      <c r="F17" s="64"/>
+      <c r="G17" s="64"/>
+      <c r="H17" s="64"/>
+      <c r="I17" s="64"/>
+      <c r="J17" s="64"/>
+      <c r="K17" s="64"/>
+      <c r="L17" s="60"/>
+      <c r="M17" s="60"/>
+      <c r="N17" s="60"/>
+    </row>
+    <row r="18" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="60"/>
+      <c r="B18" s="64"/>
+      <c r="C18" s="64"/>
+      <c r="D18" s="64"/>
+      <c r="E18" s="64"/>
+      <c r="F18" s="64"/>
+      <c r="G18" s="64"/>
+      <c r="H18" s="64"/>
+      <c r="I18" s="64"/>
+      <c r="J18" s="64"/>
+      <c r="K18" s="64"/>
+      <c r="L18" s="60"/>
+      <c r="M18" s="60"/>
+      <c r="N18" s="60"/>
+    </row>
+    <row r="19" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="60"/>
+      <c r="B19" s="64"/>
+      <c r="C19" s="64"/>
+      <c r="D19" s="64"/>
+      <c r="E19" s="64"/>
+      <c r="F19" s="64"/>
+      <c r="G19" s="64"/>
+      <c r="H19" s="64"/>
+      <c r="I19" s="64"/>
+      <c r="J19" s="64"/>
+      <c r="K19" s="64"/>
+      <c r="L19" s="60"/>
+      <c r="M19" s="60"/>
+      <c r="N19" s="60"/>
+    </row>
+    <row r="20" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="60"/>
+      <c r="B20" s="64"/>
+      <c r="C20" s="64"/>
+      <c r="D20" s="64"/>
+      <c r="E20" s="64"/>
+      <c r="F20" s="64"/>
+      <c r="G20" s="64"/>
+      <c r="H20" s="64"/>
+      <c r="I20" s="64"/>
+      <c r="J20" s="64"/>
+      <c r="K20" s="64"/>
+      <c r="L20" s="60"/>
+      <c r="M20" s="60"/>
+      <c r="N20" s="60"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="60"/>
+      <c r="B21" s="60"/>
+      <c r="C21" s="60"/>
+      <c r="D21" s="60"/>
+      <c r="E21" s="60"/>
+      <c r="F21" s="60"/>
+      <c r="G21" s="60"/>
+      <c r="H21" s="60"/>
+      <c r="I21" s="60"/>
+      <c r="J21" s="60"/>
+      <c r="K21" s="60"/>
+      <c r="L21" s="60"/>
+      <c r="M21" s="60"/>
+      <c r="N21" s="60"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B22" s="19" t="s">
         <v>110</v>
       </c>
@@ -1758,7 +2083,7 @@
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
     </row>
-    <row r="24" spans="2:11" s="18" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:14" s="18" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
